--- a/t1_confection/Secondary_Techs_Editor.xlsx
+++ b/t1_confection/Secondary_Techs_Editor.xlsx
@@ -20128,9 +20128,9 @@
     </row>
   </sheetData>
   <mergeCells count="186">
-    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A186:B186"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A98:B98"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A191:B191"/>
